--- a/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas. Il dit : c'est notre secret. Maya sent son ventre. C'est serré. C'est un malaise. Maya a peur. Maya marche vers papa. Elle prend sa main. Maya dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, à la maison, Maya le dit aussi à maman. Maman écoute. Maya se sent plus légère.</t>
+          <t>Maya joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas. C'est notre secret. Maya sent son ventre. C'est serré. C'est un malaise. Maya a peur. Maya marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, à la maison, Maya le dit aussi à maman. Maman écoute. Maya se sent plus légère.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maya joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas.
+narrateur|C'est notre secret.
+narrateur|Maya sent son ventre. C'est serré. C'est un malaise. Maya a peur. Maya marche vers papa. Elle prend sa main.
+enfant-f|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
+papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, à la maison, Maya le dit aussi à maman. Maman écoute.
+narrateur|Maya se sent plus légère.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a peur. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1835,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maya s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2002,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 narrateur|Maya se sent plus légère.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1512,7 @@
           <t>narrateur|Maya a peur. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1684,7 @@
           <t>narrateur|Maya a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1852,7 @@
           <t>narrateur|Maya s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maya raconte ce qui fait peur</t>
+          <t>Sarah raconte au bac à sable</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un seau rouge grince au bac à sable. Sarah sent son ventre. Elle raconte à papa, puis à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas. C'est notre secret. Maya sent son ventre. C'est serré. C'est un malaise. Maya a peur. Maya marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, à la maison, Maya le dit aussi à maman. Maman écoute. Maya se sent plus légère.</t>
+          <t>Un seau rouge grince un peu. L'anse est chaude au soleil. Le sable du bac est tiède. Il sent le chemin sec. Un moineau pose sur la barrière. Il fait un petit cri. L'herbe coupée sent fort. La chaussure de papa a du sable. Sarah, le seau t'attend. En ce moment, Sarah est près du bac. Elle verse le sable tout doux. Il est chaud, papa. Oui. On reste près du bac. Une voix d'adulte parle tout bas. Sarah sent son ventre. Le ventre est serré. C'est un malaise. Sarah a peur. Elle pose le seau. Elle marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Tu restes avec moi ? Oui, Sarah. Bravo. Tu as fait du bon travail. Papa tient sa main. La main de papa est chaude. Le moineau s'envole. Le seau rouge reste dans le sable. Plus tard, ils rentrent à la maison. La porte sent le bois. Maman essuie la table. Vous rentrez ? Sarah a quelque chose à dire. Sarah marche vers maman. Maman, j'ai eu peur au parc. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus légère. Bravo, Sarah. Tu as fait du bon travail. Sarah s'assoit près de maman. Papa s'assoit aussi. Le sable tombe d'une chaussure.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maya joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas.
-narrateur|C'est notre secret.
-narrateur|Maya sent son ventre. C'est serré. C'est un malaise. Maya a peur. Maya marche vers papa. Elle prend sa main.
-enfant-f|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
-papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, à la maison, Maya le dit aussi à maman. Maman écoute.
-narrateur|Maya se sent plus légère.</t>
+          <t>narrateur|Un seau rouge grince un peu.
+narrateur|L'anse est chaude au soleil.
+narrateur|Le sable du bac est tiède.
+narrateur|Il sent le chemin sec.
+narrateur|Un moineau pose sur la barrière.
+narrateur|Il fait un petit cri.
+narrateur|L'herbe coupée sent fort.
+narrateur|La chaussure de papa a du sable.
+papa|Sarah, le seau t'attend.
+narrateur|En ce moment, Sarah est près du bac.
+narrateur|Elle verse le sable tout doux.
+enfant-f|Il est chaud, papa.
+papa|Oui.
+papa|On reste près du bac.
+narrateur|Une voix d'adulte parle tout bas.
+narrateur|Sarah sent son ventre.
+narrateur|Le ventre est serré.
+narrateur|C'est un malaise.
+narrateur|Sarah a peur.
+narrateur|Elle pose le seau.
+narrateur|Elle marche vers papa.
+narrateur|Elle prend sa main.
+enfant-f|Papa, un adulte a parlé d'un secret.
+enfant-f|Mon ventre est serré.
+enfant-f|J'ai peur.
+papa|Merci de raconter.
+papa|Tu as le droit de le dire.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+papa|Je reste tout près.
+enfant-f|Tu restes avec moi ?
+papa|Oui, Sarah.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Papa tient sa main.
+narrateur|La main de papa est chaude.
+narrateur|Le moineau s'envole.
+narrateur|Le seau rouge reste dans le sable.
+narrateur|Plus tard, ils rentrent à la maison.
+narrateur|La porte sent le bois.
+narrateur|Maman essuie la table.
+maman|Vous rentrez ?
+papa|Sarah a quelque chose à dire.
+narrateur|Sarah marche vers maman.
+enfant-f|Maman, j'ai eu peur au parc.
+enfant-f|Mon ventre était serré.
+enfant-f|J'ai raconté à papa.
+maman|Merci de raconter.
+maman|Tu as le droit de le dire.
+maman|Ce qui fait peur se raconte.
+maman|On va raconter à papa ou maman.
+enfant-f|Je me sens plus légère.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+narrateur|Sarah s'assoit près de maman.
+narrateur|Papa s'assoit aussi.
+narrateur|Le sable tombe d'une chaussure.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maya a peur. Que fait-elle ?</t>
+          <t>Sarah a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1509,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maya a peur. Que fait-elle ?</t>
+          <t>narrateur|Sarah a peur.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1537,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>Sarah a senti le malaise. Elle a marché vers papa. Elle a raconté. Tu as raconté à papa ? Oui. Puis à maman aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. Le seau rouge attend au bac. La main de papa reste chaude.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1681,7 +1745,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maya a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>narrateur|Sarah a senti le malaise.
+narrateur|Elle a marché vers papa.
+narrateur|Elle a raconté.
+papa|Tu as raconté à papa ?
+enfant-f|Oui.
+maman|Puis à maman aussi.
+maman|Bravo.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+narrateur|Le seau rouge attend au bac.
+narrateur|La main de papa reste chaude.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1709,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maya s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>Sarah pose la tête contre maman. Tu es là, avec nous. On reste encore un peu ? Oui. La table sent le savon. Un grain de sable brille au sol. Tu as raconté. C'est du bon travail. Je suis près de toi. Moi aussi, je suis près. La maison est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1849,7 +1923,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maya s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>narrateur|Sarah pose la tête contre maman.
+maman|Tu es là, avec nous.
+papa|On reste encore un peu ?
+enfant-f|Oui.
+narrateur|La table sent le savon.
+narrateur|Un grain de sable brille au sol.
+maman|Tu as raconté.
+maman|C'est du bon travail.
+papa|Je suis près de toi.
+enfant-f|Moi aussi, je suis près.
+narrateur|La maison est calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1877,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le seau rouge a fini de grincer. J'ai raconté. Bravo, Sarah. On t'écoute. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2017,7 +2101,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le seau rouge a fini de grincer.
+enfant-f|J'ai raconté.
+papa|Bravo, Sarah.
+maman|On t'écoute.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2039,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un seau rouge grince un peu. L'anse est chaude au soleil. Le sable du bac est tiède. Il sent le chemin sec. Un moineau pose sur la barrière. Il fait un petit cri. L'herbe coupée sent fort. La chaussure de papa a du sable. Sarah, le seau t'attend. En ce moment, Sarah est près du bac. Elle verse le sable tout doux. Il est chaud, papa. Oui. On reste près du bac. Une voix d'adulte parle tout bas. Sarah sent son ventre. Le ventre est serré. C'est un malaise. Sarah a peur. Elle pose le seau. Elle marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Tu restes avec moi ? Oui, Sarah. Bravo. Tu as fait du bon travail. Papa tient sa main. La main de papa est chaude. Le moineau s'envole. Le seau rouge reste dans le sable. Plus tard, ils rentrent à la maison. La porte sent le bois. Maman essuie la table. Vous rentrez ? Sarah a quelque chose à dire. Sarah marche vers maman. Maman, j'ai eu peur au parc. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus légère. Bravo, Sarah. Tu as fait du bon travail. Sarah s'assoit près de maman. Papa s'assoit aussi. Le sable tombe d'une chaussure.</t>
+          <t>Un seau rouge grince un peu. L'anse est chaude au soleil. Le sable du bac est tiède. Il sent le chemin sec. Un moineau pose sur la barrière. Il fait un petit cri. L'herbe coupée sent fort. La chaussure de papa a du sable. Sarah, le seau t'attend. En ce moment, Sarah est près du bac. Elle verse le sable tout doux. Il est chaud, papa. Oui. On reste près du bac. Une voix d'adulte parle tout bas. Sarah sent son ventre. Le ventre est serré. C'est un malaise. Sarah a peur. Elle pose le seau. Elle marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Tu restes avec moi ? Oui, Sarah. Bravo. Papa tient sa main. La main de papa est chaude. Le moineau s'envole. Le seau rouge reste dans le sable. Plus tard, ils rentrent à la maison. La porte sent le bois. Maman essuie la table. Vous rentrez ? Sarah a quelque chose à dire. Sarah marche vers maman. Maman, j'ai eu peur au parc. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus légère. Bravo, Sarah. Sarah s'assoit près de maman. Papa s'assoit aussi. Le sable tombe d'une chaussure.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas. Il dit : c'est notre secret. Maya sent son ventre. C'est serré. C'est un malaise. Maya a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Maya marche vers papa. Elle prend sa main. Maya dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, à la maison, Maya le dit aussi à maman. Maman écoute. Maya se sent plus légère.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un seau rouge grince un peu. L'anse est chaude au soleil. Le sable du bac est tiède. Il sent le chemin sec. Un moineau pose sur la barrière. Il fait un petit cri. L'herbe coupée sent fort. La chaussure de papa a du sable. Sarah, le seau t'attend. En ce moment, Sarah est près du bac. Elle verse le sable tout doux. Il est chaud, papa. Oui. On reste près du bac. Une voix d'adulte parle tout bas. Sarah sent son ventre. Le ventre est serré. C'est un malaise. Sarah a peur. Elle pose le seau. Elle marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Tu restes avec moi ? Oui, Sarah. Bravo. Papa tient sa main. La main de papa est chaude. Le moineau s'envole. Le seau rouge reste dans le sable. Plus tard, ils rentrent à la maison. La porte sent le bois. Maman essuie la table. Vous rentrez ? Sarah a quelque chose à dire. Sarah marche vers maman. Maman, j'ai eu peur au parc. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus légère. Bravo, Sarah. Sarah s'assoit près de maman. Papa s'assoit aussi. Le sable tombe d'une chaussure.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1357,7 +1357,6 @@
 enfant-f|Tu restes avec moi ?
 papa|Oui, Sarah.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Papa tient sa main.
 narrateur|La main de papa est chaude.
 narrateur|Le moineau s'envole.
@@ -1377,7 +1376,6 @@
 maman|On va raconter à papa ou maman.
 enfant-f|Je me sens plus légère.
 maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
 narrateur|Sarah s'assoit près de maman.
 narrateur|Papa s'assoit aussi.
 narrateur|Le sable tombe d'une chaussure.</t>
@@ -1417,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maya a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1576,7 +1574,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1606,7 +1603,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt; se raconte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a senti le malaise. Elle a marché vers papa. Elle a raconté. Tu as raconté à papa ? Oui. Puis à maman aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. Le seau rouge attend au bac. La main de papa reste chaude.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1758,7 +1755,6 @@
 narrateur|La main de papa reste chaude.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,12 +1779,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose la tête contre maman. Tu es là, avec nous. On reste encore un peu ? Oui. La table sent le savon. Un grain de sable brille au sol. Tu as raconté. C'est du bon travail. Je suis près de toi. Moi aussi, je suis près. La maison est calme.</t>
+          <t>Sarah pose la tête contre maman. Tu es là, avec nous. On reste encore un peu ? Oui. La table sent le savon. Un grain de sable brille au sol. Tu as raconté. Je suis près de toi. Moi aussi, je suis près. La maison est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya s'assoit près de maman. Papa est là aussi. Sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est chaude.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pose la tête contre maman. Tu es là, avec nous. On reste encore un peu ? Oui. La table sent le savon. Un grain de sable brille au sol. Tu as raconté. Je suis près de toi. Moi aussi, je suis près. La maison est calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1930,13 +1926,11 @@
 narrateur|La table sent le savon.
 narrateur|Un grain de sable brille au sol.
 maman|Tu as raconté.
-maman|C'est du bon travail.
 papa|Je suis près de toi.
 enfant-f|Moi aussi, je suis près.
 narrateur|La maison est calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le seau rouge a fini de grincer. J'ai raconté. Bravo, Sarah. On t'écoute. L'histoire est finie.</t>
+          <t>Le seau rouge a fini de grincer. J'ai raconté. Bravo, Sarah. On t'écoute.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le seau rouge a fini de grincer. J'ai raconté. Bravo, Sarah. On t'écoute.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,11 +2098,9 @@
           <t>narrateur|Le seau rouge a fini de grincer.
 enfant-f|J'ai raconté.
 papa|Bravo, Sarah.
-maman|On t'écoute.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|On t'écoute.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc, bac à sable, puis maison</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maya, papa, maman</t>
+          <t>Sarah, papa, maman</t>
         </is>
       </c>
     </row>
